--- a/光伏配储项目/电价数据/2026/油坑站.xlsx
+++ b/光伏配储项目/电价数据/2026/油坑站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.4357200000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78361</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.48368</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50446</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44582</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.14211</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.08347</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.08721999999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.07285</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55622</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7408899999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.1428</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.35436</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66662</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.34589</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17943</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.02795</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3076</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40848</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45356</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7559199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.11748</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95005</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.90864</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8064600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7685700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51855</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46929</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43078</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73009</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90599</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9689500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51181</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53923</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51916</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.46664</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.52127</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.41447</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.40633</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.55313</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.02928</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.03568</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18645</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.02421</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.10226</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.59299</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.19525</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.04251</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.03907</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60163</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76564</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.79344</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18603</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.38557</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13946</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.85915</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22656</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12388</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.12273</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.87948</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.10813</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66734</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00145</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9265399999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9780800000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8115599999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33539</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52101</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42017</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45454</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48565</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22191</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.03286</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79635</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.05271</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45834</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32029</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62814</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6657799999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50415</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6284099999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46165</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34293</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52291</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03411</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.04086</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.04632</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59158</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21238</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18463</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.64115</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44196</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52607</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47416</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5215599999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41587</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33046</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.07840999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04429</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13228</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04222</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03714</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.06459999999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.06626</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.1383</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.17125</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.15057</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.14948</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.19157</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.22558</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.21584</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.20565</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.21126</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.19348</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.19378</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-0.02528</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.08505</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10149</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00596</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04541</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14076</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01025</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05262</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.23878</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.24259</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.19709</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.19926</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.24196</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7857499999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86975</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61441</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>-0.01142</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.19612</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.22798</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>-0.03764</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.13434</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8916799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.10442</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.7754500000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.26425</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.24053</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.13765</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60178</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.26968</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.15619</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.17353</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06447</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.03105</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.11862</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.21279</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.11009</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.19662</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.18891</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.13143</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.13556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>-0.01615</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>-0.02617</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.21193</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7737200000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.11121</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.01561</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.05552</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.12652</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.14912</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.17138</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.09598000000000001</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.19043</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.11292</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.19672</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.10782</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-0.04162</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.12512</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.09911</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.10998</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.16731</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.21087</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.18379</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.14936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25935</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04777</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25193</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.18556</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.21606</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.20583</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.22436</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.18039</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.13188</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.16446</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.19423</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.19001</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.08714</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.1972</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.14378</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.17766</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.20587</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.06931999999999999</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.18765</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.22479</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.02901</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.22304</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.02972</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.67096</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3652</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.0851</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.5912999999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.6851799999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.54111</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.22155</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.16621</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.08356999999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.20511</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.23251</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.10937</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.20612</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.26398</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.14969</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.07423</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.06684</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.23621</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.04586999999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.21735</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.009429999999999999</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.16102</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.22894</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.2147</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.06422</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.06512000000000001</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.08395999999999999</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.008160000000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.14615</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.00145</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.19324</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-0.02192</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-0.02737</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.18376</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.17975</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.19485</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.17512</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>-0.04052</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.17902</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.15551</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02429</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.005099999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.02108</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04801</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.15321</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.13278</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.13457</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>-0.03894</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>-0.03822</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.25172</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.005889999999999999</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.03047</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.24673</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.03232</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-0.01845</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.23766</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.09955</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-0.004990000000000001</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="R128" t="n">
+        <v>-0.00941</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.10307</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.09175</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.11081</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.12297</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.11128</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.12297</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.01726</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.07553</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.15536</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.10651</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.17038</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.15194</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.15505</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.21634</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18247</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17841</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.03015</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21687</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.13416</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.07726000000000001</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.07698000000000001</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.11356</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.16121</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.09089</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.19381</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.10901</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.19948</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.20837</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.21735</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.16776</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.14325</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.18616</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.18489</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.12181</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.20341</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.15636</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.13041</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.17379</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.09929</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.09137000000000001</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.05312</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.12203</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.02072</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.04193</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.04316</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.10692</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.09162000000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.11739</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.11185</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.08729000000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.11741</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.12066</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.20132</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.19678</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.12569</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.19809</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.19342</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.12112</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.12086</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.09312999999999999</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.08353000000000001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.12682</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.10513</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.23015</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9993300000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.54488</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.22388</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12072</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.47445</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.25574</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.24272</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.20652</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.25644</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.17745</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.19362</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.25221</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.24553</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.22963</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.10991</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.14763</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.17283</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.14592</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.03756</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.006990000000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.26809</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.04049000000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.06924</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03240999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.06519</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.07621</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.18318</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.17836</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.18153</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.09695999999999999</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.24232</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.19459</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>-0.00791</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.20627</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.24293</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.20663</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.13619</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.08288</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.10882</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.12461</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.14046</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.19856</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.14477</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.18245</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.18542</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.12072</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.11106</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.11735</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.13774</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.18419</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.05693</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.13962</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.21371</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.17711</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.08373</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>-0.03644</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.22521</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.21831</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>-0.03255</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.21856</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.21313</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.20684</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.20644</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.20711</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.20807</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.20756</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.20676</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.02065</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.20296</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.20374</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.03377</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.19629</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.19676</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.08109000000000001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.07349</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.09087999999999999</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.02092</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.20176</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.08835</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.06359000000000001</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.06122</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.19304</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.05427000000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.06889000000000001</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.11262</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.05536</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.08791</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.12558</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.15852</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.22043</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.13829</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.22136</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.16225</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.25369</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.19047</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.18547</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.20757</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.21635</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.20667</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.15233</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.15095</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.22077</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.20544</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.12066</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.08428000000000001</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.09736</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.09969</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.51168</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.20708</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.21585</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.19627</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.11589</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.23315</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.14114</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.21891</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.21605</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.21888</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.14463</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.21584</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.21685</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.13062</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.12974</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.21634</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.20441</v>
+      </c>
+      <c r="V132" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.21564</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.21337</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.21693</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.21693</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.22274</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.23674</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.21343</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.21334</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.20805</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.20874</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.19957</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.22521</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.24213</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25039</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03402</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.00338</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.00051</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20387</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15124</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24979</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.25704</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.23971</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.20011</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.17864</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.08436</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.22964</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.00587</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5317799999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.48952</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6954400000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.10192</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.1426</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-0.04161</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.02908</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.04838</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.07773000000000001</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.00571</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.25034</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.08061</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.04778</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65812</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7224299999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.03967</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.19658</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.23264</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.14849</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.20696</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.13476</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.62641</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.03431</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-0.01011</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-0.00133</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.07367</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.21863</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-0.00233</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.21829</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.21982</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.23795</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.23173</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.24517</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.15672</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.07942</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.13904</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.08365</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.17939</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.22045</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.06543</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.10762</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.03681</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.05165</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.23686</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.21872</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.22019</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.20991</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.17108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.20964</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25488</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02836</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.22153</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16147</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.10602</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.11166</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.08311</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.12592</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.21215</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.11847</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>-0.01897</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.01317</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.04157</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.05229</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.04275</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.07811</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19455</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.13426</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15611</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01429</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03835</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03561</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01149</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.16548</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.20603</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.18154</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.13534</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.20606</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.13874</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.19962</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.10431</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.08399</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.20947</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.20672</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.12483</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.09805</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.08793000000000001</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.16323</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.12949</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03827000000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>-0.03355</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21425</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75017</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87148</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16786</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00222</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04518</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.23259</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.09512999999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.17568</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.13883</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.15102</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.06267</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8382999999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.70063</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6988799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.79941</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.18141</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.14952</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.23701</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.04704</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.18617</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.08681999999999999</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.08703</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.07714</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.23767</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12442</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10992</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25304</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.22234</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.24673</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.23189</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.23653</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.20741</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.22218</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.18265</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.17215</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.11595</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.08973</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.04677000000000001</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.00292</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.02737</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.05393</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.01079</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.04237</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.04444</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.12927</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.08556999999999999</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.08910999999999999</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.08885999999999999</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.13446</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.20971</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.08828</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.10661</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.10896</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.09229000000000001</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.10551</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.11195</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.11203</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.09581000000000001</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.08753</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.09540999999999999</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.08825</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.12781</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.06197999999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.26836</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.08688</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25184</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.22266</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.18476</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.22024</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.23687</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.20877</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.23751</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.68247</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46786</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.11777</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83075</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.22063</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.15706</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.05725</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.12262</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.00722</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.11063</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.10049</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.11247</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.09036</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.02804</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.04550999999999999</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.07168000000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.14055</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.07363</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.23361</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.09423999999999999</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.09333</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.08644</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.12658</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.14643</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.14037</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.13972</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.10834</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.10067</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.10143</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.09943</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.08256000000000001</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.20885</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.02899</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.04489</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.22479</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.13066</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.20787</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.20384</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.12901</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.21863</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24286</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.21186</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.17895</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.17844</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.19427</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.20496</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.23815</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.19306</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.19309</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>-0.00766</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.64866</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.17072</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.13726</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8160599999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72274</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.12556</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.11221</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.17998</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.15805</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.06544</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.00974</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.08548</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.20069</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.20065</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.18965</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.05376</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.07654999999999999</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.04896</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.03965999999999999</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.19648</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-0.00098</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.19137</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.20509</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.21223</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.07321999999999999</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.19647</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.21032</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.20072</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03199</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17812</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01915</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.18279</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19784</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03662</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05961</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23715</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.09279000000000001</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24444</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.24862</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.24863</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.24412</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.23694</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.15847</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.12082</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42591</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.29428</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.18024</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17676</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04762</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04776</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13445</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00055</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17778</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22779</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15798</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24163</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22128</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00339</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20212</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15164</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1.40157</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>1.34284</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>1.36879</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1.32829</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.33561</v>
       </c>
     </row>
   </sheetData>
